--- a/assets/templates/mof_r3_excel.xlsx
+++ b/assets/templates/mof_r3_excel.xlsx
@@ -68,14 +68,19 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7562850" cy="10696575"/>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="f9f95d16-85cf-48f6-aa09-3209d9870256">
@@ -102,7 +107,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -300,76 +305,86 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AU70"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="12" width="9" customWidth="1"/>
+    <col min="1" max="47" width="1.714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="20" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="31" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="34" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="35" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="50" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="53" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="54" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" ht="12" customHeight="1"/>
+    <row r="2" ht="12" customHeight="1"/>
+    <row r="3" ht="12" customHeight="1"/>
+    <row r="4" ht="12" customHeight="1"/>
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="12" customHeight="1"/>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="12" customHeight="1"/>
+    <row r="9" ht="12" customHeight="1"/>
+    <row r="10" ht="12" customHeight="1"/>
+    <row r="11" ht="12" customHeight="1"/>
+    <row r="12" ht="12" customHeight="1"/>
+    <row r="13" ht="12" customHeight="1"/>
+    <row r="14" ht="12" customHeight="1"/>
+    <row r="15" ht="12" customHeight="1"/>
+    <row r="16" ht="12" customHeight="1"/>
+    <row r="17" ht="12" customHeight="1"/>
+    <row r="18" ht="12" customHeight="1"/>
+    <row r="19" ht="12" customHeight="1"/>
+    <row r="20" ht="12" customHeight="1"/>
+    <row r="21" ht="12" customHeight="1"/>
+    <row r="22" ht="12" customHeight="1"/>
+    <row r="23" ht="12" customHeight="1"/>
+    <row r="24" ht="12" customHeight="1"/>
+    <row r="25" ht="12" customHeight="1"/>
+    <row r="26" ht="12" customHeight="1"/>
+    <row r="27" ht="12" customHeight="1"/>
+    <row r="28" ht="12" customHeight="1"/>
+    <row r="29" ht="12" customHeight="1"/>
+    <row r="30" ht="12" customHeight="1"/>
+    <row r="31" ht="12" customHeight="1"/>
+    <row r="32" ht="12" customHeight="1"/>
+    <row r="33" ht="12" customHeight="1"/>
+    <row r="34" ht="12" customHeight="1"/>
+    <row r="35" ht="12" customHeight="1"/>
+    <row r="36" ht="12" customHeight="1"/>
+    <row r="37" ht="12" customHeight="1"/>
+    <row r="38" ht="12" customHeight="1"/>
+    <row r="39" ht="12" customHeight="1"/>
+    <row r="40" ht="12" customHeight="1"/>
+    <row r="41" ht="12" customHeight="1"/>
+    <row r="42" ht="12" customHeight="1"/>
+    <row r="43" ht="12" customHeight="1"/>
+    <row r="44" ht="12" customHeight="1"/>
+    <row r="45" ht="12" customHeight="1"/>
+    <row r="46" ht="12" customHeight="1"/>
+    <row r="47" ht="12" customHeight="1"/>
+    <row r="48" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
+    <row r="65" ht="12" customHeight="1"/>
+    <row r="66" ht="12" customHeight="1"/>
+    <row r="67" ht="12" customHeight="1"/>
+    <row r="68" ht="12" customHeight="1"/>
+    <row r="69" ht="12" customHeight="1"/>
+    <row r="70" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="1"/>

--- a/assets/templates/mof_r3_excel.xlsx
+++ b/assets/templates/mof_r3_excel.xlsx
@@ -312,7 +312,7 @@
   <dimension ref="A1:AU70"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="47" width="1.714" customWidth="1"/>
+    <col min="1" max="47" width="2.372" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1"/>
